--- a/data/gravel/Lynskey Odyssey 2025.xlsx
+++ b/data/gravel/Lynskey Odyssey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADAF1CF-541D-7146-9417-CD9FE7CCFDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD95AD9-B4B8-B54A-B3CD-D76BF459F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -347,9 +347,6 @@
     <t>Odyssey</t>
   </si>
   <si>
-    <t>https://lynskeyperformance.com/products/odyssey-gravel-frame</t>
-  </si>
-  <si>
     <t>rider_min_spec</t>
   </si>
   <si>
@@ -369,6 +366,12 @@
   </si>
   <si>
     <t>usd</t>
+  </si>
+  <si>
+    <t>https://lynskeyperformance.com/collections/odyssey</t>
+  </si>
+  <si>
+    <t>https://lynskeyperformance.com/cdn/shop/files/DSC_7170.jpg?v=1757702602&amp;width=416</t>
   </si>
 </sst>
 </file>
@@ -768,7 +771,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -776,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="23" x14ac:dyDescent="0.3">
@@ -784,7 +792,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>76</v>
@@ -1061,7 +1069,7 @@
     </row>
     <row r="22" spans="1:6" ht="23" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>101</v>
@@ -1230,7 +1238,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C33">
         <v>152</v>
@@ -1247,7 +1255,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34">
         <v>157</v>
@@ -1340,7 +1348,7 @@
         <v>36</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1515,7 +1523,7 @@
         <v>69</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Lynskey Odyssey 2025.xlsx
+++ b/data/gravel/Lynskey Odyssey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD95AD9-B4B8-B54A-B3CD-D76BF459F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFA6AC2-E3F3-884B-A7DA-20E6ADDD2860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -365,13 +365,19 @@
     <t>size</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>https://lynskeyperformance.com/collections/odyssey</t>
   </si>
   <si>
     <t>https://lynskeyperformance.com/cdn/shop/files/DSC_7170.jpg?v=1757702602&amp;width=416</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Chattanooga, Tennessee, USA</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -771,12 +777,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1523,7 +1529,15 @@
         <v>69</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Lynskey Odyssey 2025.xlsx
+++ b/data/gravel/Lynskey Odyssey 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFA6AC2-E3F3-884B-A7DA-20E6ADDD2860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C062020-6DEB-794C-B459-BA6254AE53D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,24 @@
   </si>
   <si>
     <t>Chattanooga, Tennessee, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -733,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1407,136 +1425,166 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="1"/>
+        <v>118</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
-      </c>
-      <c r="B71">
-        <v>2895</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>113</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>114</v>
       </c>
     </row>
